--- a/sheets/민요/검수/신 천안 삼거리.xlsx
+++ b/sheets/민요/검수/신 천안 삼거리.xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +176,42 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3791,8 +3907,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:M18"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -3807,978 +3927,1043 @@
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신 천안 삼거리 — 민요채보-1/신 천안 삼거리.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">신 천안 삼거리</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="H3" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">제</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="J3" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">천</t>
         </is>
       </c>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="L3" s="14"/>
+      <c r="M3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">천</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">까</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="E4" s="17"/>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 仲</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="G4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">까</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">멋</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="J4" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">안</t>
         </is>
       </c>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="L4" s="13"/>
+      <c r="M4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">안</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2" t="inlineStr">
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C5" s="17"/>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E5" s="17"/>
+      <c r="F5" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">청</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="H5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="J5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
       </c>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="L5" s="13"/>
+      <c r="M5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="C6" s="18"/>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 仲</t>
-        </is>
-      </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="E6" s="18"/>
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">춤</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="J6" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 仲</t>
-        </is>
-      </c>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="K6" s="18"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">삼</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J7" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">거</t>
         </is>
       </c>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="L7" s="13"/>
+      <c r="M7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">거</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2" t="inlineStr">
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="13"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E8" s="17"/>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G8" s="17"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="J8" s="13"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 仲</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-―
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">潢
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 仲</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="G9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J9" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">능</t>
         </is>
       </c>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="L9" s="13"/>
+      <c r="M9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">흥</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="E10" s="18"/>
+      <c r="F10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 仲
 姑</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 仲</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="J10" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K10" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">수</t>
         </is>
       </c>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="L10" s="13"/>
+      <c r="M10" s="18"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">족</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="H11" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">족</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="J11" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">능</t>
         </is>
       </c>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="L11" s="13"/>
+      <c r="M11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">능</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 無</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="G12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="J12" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="K12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">수</t>
         </is>
       </c>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="L12" s="13"/>
+      <c r="M12" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">수</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C13" s="17"/>
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">열</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="J13" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">버</t>
         </is>
       </c>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="L13" s="13"/>
+      <c r="M13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">버</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="48" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 仲</t>
-        </is>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+          </r>
+        </is>
+      </c>
+      <c r="C14" s="18"/>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 仲</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="E14" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="H14" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 仲</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="I14" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J14" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無
 無</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K14" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">들</t>
         </is>
       </c>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="L14" s="13"/>
+      <c r="M14" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">들</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="1">
-        <v>13</v>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
+    <row r="15" ht="56" customHeight="1">
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="H15" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">음</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="J15" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
       </c>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="L15" s="13"/>
+      <c r="M15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="1">
-        <v>14</v>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+    <row r="16" ht="56" customHeight="1">
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 仲</t>
-        </is>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+          </r>
+        </is>
+      </c>
+      <c r="C16" s="17"/>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 仲</t>
-        </is>
-      </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+          </r>
+        </is>
+      </c>
+      <c r="E16" s="17"/>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G16" s="17"/>
+      <c r="H16" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 仲</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="I16" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-    </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="1">
-        <v>15</v>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="J16" s="13" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="K16" s="17"/>
+      <c r="L16" s="13"/>
+      <c r="M16" s="17"/>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="H17" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">음</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J17" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">음</t>
         </is>
       </c>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="1">
-        <v>16</v>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="L17" s="13"/>
+      <c r="M17" s="17"/>
+    </row>
+    <row r="18" ht="56" customHeight="1">
+      <c r="B18" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">○</t>
         </is>
       </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C18" s="18"/>
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">○</t>
         </is>
       </c>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="E18" s="18"/>
+      <c r="F18" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">○</t>
         </is>
       </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="G18" s="18"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J18" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
+      <c r="K18" s="18"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="18"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:M2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="77"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/신 천안 삼거리.xlsx
+++ b/sheets/민요/검수/신 천안 삼거리.xlsx
@@ -409,7 +409,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -628,13 +628,13 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―仲</t>
+          <t xml:space="preserve">姑|–仲</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―仲</t>
+–仲</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -703,13 +703,13 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―</t>
+          <t xml:space="preserve">南|–</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -743,12 +743,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I7" s="2"/>
@@ -778,13 +778,13 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|―</t>
+          <t xml:space="preserve">–|–</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―</t>
+          <t xml:space="preserve">–
+–</t>
         </is>
       </c>
       <c r="I8" s="2"/>
@@ -932,13 +932,13 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―無</t>
+          <t xml:space="preserve">潢|–無</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―無</t>
+–無</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1007,13 +1007,13 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―</t>
+          <t xml:space="preserve">南|–</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1047,12 +1047,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I15" s="2"/>
@@ -1240,13 +1240,13 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―仲</t>
+          <t xml:space="preserve">姑|–仲</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―仲</t>
+–仲</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1323,13 +1323,13 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―</t>
+          <t xml:space="preserve">南|–</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -1557,13 +1557,13 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|―南</t>
+          <t xml:space="preserve">無|–南</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―南</t>
+–南</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1636,13 +1636,13 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―南</t>
+          <t xml:space="preserve">姑|–南</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―南</t>
+–南</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -1715,13 +1715,13 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―</t>
+          <t xml:space="preserve">姑|–</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -1790,13 +1790,13 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌|―湳</t>
+          <t xml:space="preserve">㴌|–湳</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
-―湳</t>
+–湳</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -1865,13 +1865,13 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|―㴌</t>
+          <t xml:space="preserve">㳞|–㴌</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-―㴌</t>
+–㴌</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -1944,13 +1944,13 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌|―</t>
+          <t xml:space="preserve">㴌|–</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
-―</t>
+–</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -1984,12 +1984,12 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I39" s="2"/>
@@ -2019,13 +2019,13 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌|―湳</t>
+          <t xml:space="preserve">㴌|–湳</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
-―湳</t>
+–湳</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -2177,13 +2177,13 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―無</t>
+          <t xml:space="preserve">潢|–無</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―無</t>
+–無</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -2256,13 +2256,13 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―</t>
+          <t xml:space="preserve">南|–</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I47" s="2"/>
@@ -2489,13 +2489,13 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―仲</t>
+          <t xml:space="preserve">姑|–仲</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―仲</t>
+–仲</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -2568,13 +2568,13 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―</t>
+          <t xml:space="preserve">南|–</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -2801,13 +2801,13 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|―南</t>
+          <t xml:space="preserve">無|–南</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―南</t>
+–南</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -2880,13 +2880,13 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―南</t>
+          <t xml:space="preserve">姑|–南</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―南</t>
+–南</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -2955,13 +2955,13 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―</t>
+          <t xml:space="preserve">姑|–</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -3064,7 +3064,7 @@
       <c r="D3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
-―湳</t>
+–湳</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
@@ -3143,7 +3143,7 @@
       <c r="B5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―仲</t>
+–仲</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -3154,7 +3154,7 @@
       <c r="D5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-―㴌</t>
+–㴌</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -3165,7 +3165,7 @@
       <c r="F5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―仲</t>
+–仲</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr">
@@ -3176,7 +3176,7 @@
       <c r="H5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―仲</t>
+–仲</t>
         </is>
       </c>
       <c r="I5" s="9" t="inlineStr">
@@ -3233,7 +3233,7 @@
       <c r="B7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -3244,7 +3244,7 @@
       <c r="D7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
-―</t>
+–</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -3255,7 +3255,7 @@
       <c r="F7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
@@ -3266,7 +3266,7 @@
       <c r="H7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr">
@@ -3287,20 +3287,20 @@
       <c r="C8" s="9"/>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E8" s="9"/>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
       <c r="G8" s="9"/>
       <c r="H8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I8" s="9"/>
@@ -3323,7 +3323,7 @@
       <c r="D9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
-―湳</t>
+–湳</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
@@ -3344,8 +3344,8 @@
       </c>
       <c r="H9" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―</t>
+          <t xml:space="preserve">–
+–</t>
         </is>
       </c>
       <c r="I9" s="9"/>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="D12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―無</t>
+          <t xml:space="preserve">–無</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
@@ -3492,7 +3492,7 @@
       <c r="B13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―南</t>
+–南</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
@@ -3503,7 +3503,7 @@
       <c r="D13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―無</t>
+–無</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -3514,7 +3514,7 @@
       <c r="F13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―南</t>
+–南</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
@@ -3525,7 +3525,7 @@
       <c r="H13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―無</t>
+–無</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr">
@@ -3582,7 +3582,7 @@
       <c r="B15" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―南</t>
+–南</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -3593,7 +3593,7 @@
       <c r="D15" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -3604,7 +3604,7 @@
       <c r="F15" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―南</t>
+–南</t>
         </is>
       </c>
       <c r="G15" s="8" t="inlineStr">
@@ -3615,7 +3615,7 @@
       <c r="H15" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I15" s="8" t="inlineStr">
@@ -3636,7 +3636,7 @@
       <c r="C16" s="9"/>
       <c r="D16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E16" s="9"/>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="H16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I16" s="9"/>
@@ -3664,7 +3664,7 @@
       <c r="B17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
@@ -3686,7 +3686,7 @@
       <c r="F17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr">

--- a/sheets/민요/검수/신 천안 삼거리.xlsx
+++ b/sheets/민요/검수/신 천안 삼거리.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,30 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3033,717 +3071,717 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">신 천안 삼거리</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아까</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 –湳</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">우정</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">제멋</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">천안</t>
         </is>
       </c>
-      <c r="J3" s="17"/>
-      <c r="K3" s="8"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="22"/>
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">운</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="E4" s="23"/>
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="J4" s="17"/>
-      <c r="K4" s="9"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="23"/>
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –仲</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">청</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 –㴌</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –仲</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">겨</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –仲</t>
         </is>
       </c>
-      <c r="I5" s="9" t="inlineStr">
+      <c r="I5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">삼거</t>
         </is>
       </c>
-      <c r="J5" s="17"/>
-      <c r="K5" s="9"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="23"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑仲</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">춘</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">월</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="F6" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">姑仲</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G6" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">워</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑仲</t>
         </is>
       </c>
-      <c r="I6" s="10"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="10"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="24"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 –</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="I7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="J7" s="17"/>
-      <c r="K7" s="8"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="22"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="C8" s="23"/>
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E8" s="9"/>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="E8" s="23"/>
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="G8" s="9"/>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="G8" s="23"/>
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I8" s="9"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="9"/>
+      <c r="I8" s="23"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="23"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢
 無南</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">이이</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 –湳</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">아아</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢
 無南</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">어어</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –</t>
         </is>
       </c>
-      <c r="I9" s="9"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="9"/>
+      <c r="I9" s="23"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="23"/>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">이이</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞㴌</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">아아</t>
         </is>
       </c>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="G10" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">어어</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I10" s="10"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="10"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="24"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 南</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">다늙</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">오고</t>
         </is>
       </c>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 南</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">축늘</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="I11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">능수</t>
         </is>
       </c>
-      <c r="J11" s="17"/>
-      <c r="K11" s="8"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="22"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–無</t>
         </is>
       </c>
-      <c r="E12" s="9" t="inlineStr">
+      <c r="E12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
       </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="G12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="H12" s="18" t="inlineStr">
+      <c r="H12" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I12" s="12" t="inlineStr">
+      <c r="I12" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="J12" s="17"/>
-      <c r="K12" s="9"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="23"/>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –南</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –無</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">가지</t>
         </is>
       </c>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –南</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">졌구</t>
         </is>
       </c>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –無</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="I13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">버들</t>
         </is>
       </c>
-      <c r="J13" s="17"/>
-      <c r="K13" s="9"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="23"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">노</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">마</t>
         </is>
       </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="G14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="10"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="24"/>
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="0"/>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –南</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="F15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –南</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="G15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">음으</t>
         </is>
       </c>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="H15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="I15" s="8" t="inlineStr">
+      <c r="I15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
       </c>
-      <c r="J15" s="17"/>
-      <c r="K15" s="8"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="22"/>
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="0"/>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="C16" s="23"/>
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E16" s="9"/>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="E16" s="23"/>
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G16" s="9" t="inlineStr">
+      <c r="G16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">으</t>
         </is>
       </c>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="H16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I16" s="9"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="9"/>
+      <c r="I16" s="23"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="23"/>
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="0"/>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢
 無南</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">아아</t>
         </is>
       </c>
-      <c r="F17" s="17" t="inlineStr">
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="G17" s="9" t="inlineStr">
+      <c r="G17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">응</t>
         </is>
       </c>
-      <c r="H17" s="17" t="inlineStr">
+      <c r="H17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無潢
 無南</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr">
+      <c r="I17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">응응</t>
         </is>
       </c>
-      <c r="J17" s="17"/>
-      <c r="K17" s="9"/>
+      <c r="J17" s="21"/>
+      <c r="K17" s="23"/>
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="0"/>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="C18" s="24"/>
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G18" s="10"/>
-      <c r="H18" s="17" t="inlineStr">
+      <c r="G18" s="24"/>
+      <c r="H18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I18" s="10" t="inlineStr">
+      <c r="I18" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">응</t>
         </is>
       </c>
-      <c r="J18" s="17"/>
-      <c r="K18" s="10"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/신 천안 삼거리.xlsx
+++ b/sheets/민요/검수/신 천안 삼거리.xlsx
@@ -3054,22 +3054,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="55.19" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
       <c r="J2" s="20"/>
       <c r="K2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="55.19" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
       <c r="J3" s="21"/>
       <c r="K3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
       <c r="J4" s="21"/>
       <c r="K4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
       <c r="J5" s="21"/>
       <c r="K5" s="23"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
       <c r="J6" s="21"/>
       <c r="K6" s="24"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3315,11 +3315,11 @@
       <c r="J7" s="21"/>
       <c r="K7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C8" s="23"/>
@@ -3345,7 +3345,7 @@
       <c r="J8" s="21"/>
       <c r="K8" s="23"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
       <c r="J9" s="21"/>
       <c r="K9" s="23"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -3431,7 +3431,7 @@
       <c r="J10" s="21"/>
       <c r="K10" s="24"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       <c r="J11" s="21"/>
       <c r="K11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
       <c r="J12" s="21"/>
       <c r="K12" s="23"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
       <c r="J13" s="21"/>
       <c r="K13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
       <c r="J14" s="21"/>
       <c r="K14" s="24"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="55.19" customHeight="1">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
       <c r="J15" s="21"/>
       <c r="K15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="55.19" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
       <c r="J16" s="21"/>
       <c r="K16" s="23"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="55.19" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
       <c r="J17" s="21"/>
       <c r="K17" s="23"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="55.19" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>

--- a/sheets/민요/검수/신 천안 삼거리.xlsx
+++ b/sheets/민요/검수/신 천안 삼거리.xlsx
@@ -3096,7 +3096,8 @@
       </c>
       <c r="C3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">아까</t>
+          <t xml:space="preserve">아
+까</t>
         </is>
       </c>
       <c r="D3" s="21" t="inlineStr">
@@ -3107,7 +3108,8 @@
       </c>
       <c r="E3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">우정</t>
+          <t xml:space="preserve">우
+정</t>
         </is>
       </c>
       <c r="F3" s="21" t="inlineStr">
@@ -3118,7 +3120,8 @@
       </c>
       <c r="G3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">제멋</t>
+          <t xml:space="preserve">제
+멋</t>
         </is>
       </c>
       <c r="H3" s="21" t="inlineStr">
@@ -3129,7 +3132,8 @@
       </c>
       <c r="I3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">천안</t>
+          <t xml:space="preserve">천
+안</t>
         </is>
       </c>
       <c r="J3" s="21"/>
@@ -3219,7 +3223,8 @@
       </c>
       <c r="I5" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">삼거</t>
+          <t xml:space="preserve">삼
+거</t>
         </is>
       </c>
       <c r="J5" s="21"/>
@@ -3355,7 +3360,8 @@
       </c>
       <c r="C9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">이이</t>
+          <t xml:space="preserve">이
+이</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -3366,7 +3372,8 @@
       </c>
       <c r="E9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">아아</t>
+          <t xml:space="preserve">아
+아</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -3377,7 +3384,8 @@
       </c>
       <c r="G9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">어어</t>
+          <t xml:space="preserve">어
+어</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -3399,7 +3407,8 @@
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">이이</t>
+          <t xml:space="preserve">이
+이</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -3409,7 +3418,8 @@
       </c>
       <c r="E10" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">아아</t>
+          <t xml:space="preserve">아
+아</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr">
@@ -3419,7 +3429,8 @@
       </c>
       <c r="G10" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">어어</t>
+          <t xml:space="preserve">어
+어</t>
         </is>
       </c>
       <c r="H10" s="21" t="inlineStr">
@@ -3441,7 +3452,8 @@
       </c>
       <c r="C11" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">다늙</t>
+          <t xml:space="preserve">다
+늙</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -3452,7 +3464,8 @@
       </c>
       <c r="E11" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">오고</t>
+          <t xml:space="preserve">오
+고</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
@@ -3463,7 +3476,8 @@
       </c>
       <c r="G11" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">축늘</t>
+          <t xml:space="preserve">축
+늘</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
@@ -3474,7 +3488,8 @@
       </c>
       <c r="I11" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">능수</t>
+          <t xml:space="preserve">능
+수</t>
         </is>
       </c>
       <c r="J11" s="21"/>
@@ -3546,7 +3561,8 @@
       </c>
       <c r="E13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">가지</t>
+          <t xml:space="preserve">가
+지</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr">
@@ -3557,7 +3573,8 @@
       </c>
       <c r="G13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">졌구</t>
+          <t xml:space="preserve">졌
+구</t>
         </is>
       </c>
       <c r="H13" s="21" t="inlineStr">
@@ -3568,7 +3585,8 @@
       </c>
       <c r="I13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">버들</t>
+          <t xml:space="preserve">버
+들</t>
         </is>
       </c>
       <c r="J13" s="21"/>
@@ -3647,7 +3665,8 @@
       </c>
       <c r="G15" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">음으</t>
+          <t xml:space="preserve">음
+으</t>
         </is>
       </c>
       <c r="H15" s="21" t="inlineStr">
@@ -3718,7 +3737,8 @@
       </c>
       <c r="E17" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">아아</t>
+          <t xml:space="preserve">아
+아</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr">
@@ -3740,7 +3760,8 @@
       </c>
       <c r="I17" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">응응</t>
+          <t xml:space="preserve">응
+응</t>
         </is>
       </c>
       <c r="J17" s="21"/>

--- a/sheets/민요/검수/신 천안 삼거리.xlsx
+++ b/sheets/민요/검수/신 천안 삼거리.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -233,6 +238,21 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3094,7 +3114,7 @@
 仲</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">아
 까</t>
@@ -3106,7 +3126,7 @@
 –湳</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">우
 정</t>
@@ -3118,7 +3138,7 @@
 仲</t>
         </is>
       </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="G3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">제
 멋</t>
@@ -3130,14 +3150,14 @@
 姑</t>
         </is>
       </c>
-      <c r="I3" s="22" t="inlineStr">
+      <c r="I3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">천
 안</t>
         </is>
       </c>
       <c r="J3" s="21"/>
-      <c r="K3" s="22"/>
+      <c r="K3" s="28"/>
     </row>
     <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
@@ -3146,7 +3166,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="C4" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">운</t>
         </is>
@@ -3156,13 +3176,13 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E4" s="23"/>
+      <c r="E4" s="29"/>
       <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G4" s="23" t="inlineStr">
+      <c r="G4" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -3172,13 +3192,13 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I4" s="23" t="inlineStr">
+      <c r="I4" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
       <c r="J4" s="21"/>
-      <c r="K4" s="23"/>
+      <c r="K4" s="29"/>
     </row>
     <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
@@ -3188,7 +3208,7 @@
 –仲</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">청</t>
         </is>
@@ -3199,7 +3219,7 @@
 –㴌</t>
         </is>
       </c>
-      <c r="E5" s="23" t="inlineStr">
+      <c r="E5" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
@@ -3210,7 +3230,7 @@
 –仲</t>
         </is>
       </c>
-      <c r="G5" s="23" t="inlineStr">
+      <c r="G5" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">겨</t>
         </is>
@@ -3221,14 +3241,14 @@
 –仲</t>
         </is>
       </c>
-      <c r="I5" s="23" t="inlineStr">
+      <c r="I5" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">삼
 거</t>
         </is>
       </c>
       <c r="J5" s="21"/>
-      <c r="K5" s="23"/>
+      <c r="K5" s="29"/>
     </row>
     <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
@@ -3237,7 +3257,7 @@
           <t xml:space="preserve">姑仲</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">춘</t>
         </is>
@@ -3247,7 +3267,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E6" s="24" t="inlineStr">
+      <c r="E6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">월</t>
         </is>
@@ -3257,7 +3277,7 @@
           <t xml:space="preserve">姑仲</t>
         </is>
       </c>
-      <c r="G6" s="26" t="inlineStr">
+      <c r="G6" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">워</t>
         </is>
@@ -3267,9 +3287,9 @@
           <t xml:space="preserve">姑仲</t>
         </is>
       </c>
-      <c r="I6" s="24"/>
+      <c r="I6" s="30"/>
       <c r="J6" s="21"/>
-      <c r="K6" s="24"/>
+      <c r="K6" s="30"/>
     </row>
     <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
@@ -3279,7 +3299,7 @@
 –</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -3290,7 +3310,7 @@
 –</t>
         </is>
       </c>
-      <c r="E7" s="22" t="inlineStr">
+      <c r="E7" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -3301,7 +3321,7 @@
 –</t>
         </is>
       </c>
-      <c r="G7" s="22" t="inlineStr">
+      <c r="G7" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
@@ -3312,13 +3332,13 @@
 –</t>
         </is>
       </c>
-      <c r="I7" s="22" t="inlineStr">
+      <c r="I7" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
       <c r="J7" s="21"/>
-      <c r="K7" s="22"/>
+      <c r="K7" s="28"/>
     </row>
     <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
@@ -3327,28 +3347,28 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C8" s="23"/>
+      <c r="C8" s="29"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E8" s="23"/>
+      <c r="E8" s="29"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="G8" s="23"/>
+      <c r="G8" s="29"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I8" s="23"/>
+      <c r="I8" s="29"/>
       <c r="J8" s="21"/>
-      <c r="K8" s="23"/>
+      <c r="K8" s="29"/>
     </row>
     <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
@@ -3358,7 +3378,7 @@
 無南</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">이
 이</t>
@@ -3370,7 +3390,7 @@
 –湳</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">아
 아</t>
@@ -3382,7 +3402,7 @@
 無南</t>
         </is>
       </c>
-      <c r="G9" s="23" t="inlineStr">
+      <c r="G9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">어
 어</t>
@@ -3394,9 +3414,9 @@
 –</t>
         </is>
       </c>
-      <c r="I9" s="23"/>
+      <c r="I9" s="29"/>
       <c r="J9" s="21"/>
-      <c r="K9" s="23"/>
+      <c r="K9" s="29"/>
     </row>
     <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
@@ -3405,7 +3425,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">이
 이</t>
@@ -3416,7 +3436,7 @@
           <t xml:space="preserve">㳞㴌</t>
         </is>
       </c>
-      <c r="E10" s="24" t="inlineStr">
+      <c r="E10" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">아
 아</t>
@@ -3427,7 +3447,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G10" s="24" t="inlineStr">
+      <c r="G10" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">어
 어</t>
@@ -3438,9 +3458,9 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I10" s="24"/>
+      <c r="I10" s="30"/>
       <c r="J10" s="21"/>
-      <c r="K10" s="24"/>
+      <c r="K10" s="30"/>
     </row>
     <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
@@ -3450,7 +3470,7 @@
 南</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">다
 늙</t>
@@ -3462,7 +3482,7 @@
 潢</t>
         </is>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E11" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">오
 고</t>
@@ -3474,7 +3494,7 @@
 南</t>
         </is>
       </c>
-      <c r="G11" s="22" t="inlineStr">
+      <c r="G11" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">축
 늘</t>
@@ -3486,14 +3506,14 @@
 無</t>
         </is>
       </c>
-      <c r="I11" s="22" t="inlineStr">
+      <c r="I11" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">능
 수</t>
         </is>
       </c>
       <c r="J11" s="21"/>
-      <c r="K11" s="22"/>
+      <c r="K11" s="28"/>
     </row>
     <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
@@ -3502,7 +3522,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -3512,7 +3532,7 @@
           <t xml:space="preserve">–無</t>
         </is>
       </c>
-      <c r="E12" s="23" t="inlineStr">
+      <c r="E12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">오</t>
         </is>
@@ -3522,7 +3542,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G12" s="23" t="inlineStr">
+      <c r="G12" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -3532,13 +3552,13 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I12" s="27" t="inlineStr">
+      <c r="I12" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
       <c r="J12" s="21"/>
-      <c r="K12" s="23"/>
+      <c r="K12" s="29"/>
     </row>
     <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
@@ -3548,7 +3568,7 @@
 –南</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -3559,7 +3579,7 @@
 –無</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="E13" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">가
 지</t>
@@ -3571,7 +3591,7 @@
 –南</t>
         </is>
       </c>
-      <c r="G13" s="23" t="inlineStr">
+      <c r="G13" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">졌
 구</t>
@@ -3583,14 +3603,14 @@
 –無</t>
         </is>
       </c>
-      <c r="I13" s="23" t="inlineStr">
+      <c r="I13" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">버
 들</t>
         </is>
       </c>
       <c r="J13" s="21"/>
-      <c r="K13" s="23"/>
+      <c r="K13" s="29"/>
     </row>
     <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
@@ -3599,7 +3619,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">노</t>
         </is>
@@ -3609,7 +3629,7 @@
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="E14" s="24" t="inlineStr">
+      <c r="E14" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">마</t>
         </is>
@@ -3619,7 +3639,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G14" s="24" t="inlineStr">
+      <c r="G14" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -3629,9 +3649,9 @@
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="I14" s="24"/>
+      <c r="I14" s="30"/>
       <c r="J14" s="21"/>
-      <c r="K14" s="24"/>
+      <c r="K14" s="30"/>
     </row>
     <row r="15" ht="55.19" customHeight="1">
       <c r="A15" s="0"/>
@@ -3641,7 +3661,7 @@
 –南</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
@@ -3652,7 +3672,7 @@
 –</t>
         </is>
       </c>
-      <c r="E15" s="22" t="inlineStr">
+      <c r="E15" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
@@ -3663,7 +3683,7 @@
 –南</t>
         </is>
       </c>
-      <c r="G15" s="22" t="inlineStr">
+      <c r="G15" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">음
 으</t>
@@ -3675,13 +3695,13 @@
 –</t>
         </is>
       </c>
-      <c r="I15" s="22" t="inlineStr">
+      <c r="I15" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
       </c>
       <c r="J15" s="21"/>
-      <c r="K15" s="22"/>
+      <c r="K15" s="28"/>
     </row>
     <row r="16" ht="55.19" customHeight="1">
       <c r="A16" s="0"/>
@@ -3690,19 +3710,19 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C16" s="23"/>
+      <c r="C16" s="29"/>
       <c r="D16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E16" s="23"/>
+      <c r="E16" s="29"/>
       <c r="F16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G16" s="23" t="inlineStr">
+      <c r="G16" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">으</t>
         </is>
@@ -3712,9 +3732,9 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I16" s="23"/>
+      <c r="I16" s="29"/>
       <c r="J16" s="21"/>
-      <c r="K16" s="23"/>
+      <c r="K16" s="29"/>
     </row>
     <row r="17" ht="55.19" customHeight="1">
       <c r="A17" s="0"/>
@@ -3724,7 +3744,7 @@
 –</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C17" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -3735,7 +3755,7 @@
 無南</t>
         </is>
       </c>
-      <c r="E17" s="23" t="inlineStr">
+      <c r="E17" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">아
 아</t>
@@ -3747,7 +3767,7 @@
 –</t>
         </is>
       </c>
-      <c r="G17" s="23" t="inlineStr">
+      <c r="G17" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">응</t>
         </is>
@@ -3758,14 +3778,14 @@
 無南</t>
         </is>
       </c>
-      <c r="I17" s="23" t="inlineStr">
+      <c r="I17" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">응
 응</t>
         </is>
       </c>
       <c r="J17" s="21"/>
-      <c r="K17" s="23"/>
+      <c r="K17" s="29"/>
     </row>
     <row r="18" ht="55.19" customHeight="1">
       <c r="A18" s="0"/>
@@ -3774,13 +3794,13 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C18" s="24"/>
+      <c r="C18" s="30"/>
       <c r="D18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E18" s="24" t="inlineStr">
+      <c r="E18" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -3790,19 +3810,19 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G18" s="24"/>
+      <c r="G18" s="30"/>
       <c r="H18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I18" s="24" t="inlineStr">
+      <c r="I18" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">응</t>
         </is>
       </c>
       <c r="J18" s="21"/>
-      <c r="K18" s="24"/>
+      <c r="K18" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/신 천안 삼거리.xlsx
+++ b/sheets/민요/검수/신 천안 삼거리.xlsx
@@ -399,7 +399,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 16정간 인쇄 양식(번호 1~16)이지만 가로선 없이 번호 2개(1·2, 3·4 …)씩 큰 칸 8개로 쓰고 칸마다 율명 3개(굿거리 3소박) → 큰 칸 1개 = 정간 1개, 8정간 4/4. 인쇄 줄 1·6~8은 비어 제외, 인쇄 줄 2~5 = 줄1~4. 이 손글씨의 南은 古처럼 흘려 씀. 3줄 앞부분은 청성(㴌湳㳞). 가사는 각 율명 줄 오른쪽 칸. 하단 양식번호 "196" 무시.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 16정간 인쇄 양식(번호 1~16)이지만 가로선 없이 번호 2개(1·2, 3·4 …)씩 큰 칸 8개로 쓰고 칸마다 율명 3개(굿거리 3소박) → 큰 칸 1개 = 정간 1개, 8정간 4/4. 인쇄 줄 1·6~8은 비어 제외, 인쇄 줄 2~5 = 줄1~4. 이 손글씨의 南은 古처럼 흘려 씀. 3줄 앞부분은 청성(㴌湳㳞). 가사는 각 율명 줄 오른쪽 칸. 하단 양식번호 "196" 무시. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
@@ -747,14 +747,14 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|無|潢</t>
+          <t xml:space="preserve">無|無|㴌</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 無
-潢</t>
+㴌</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
         <is>
           <t xml:space="preserve">無
 無
-潢</t>
+㴌</t>
         </is>
       </c>
       <c r="I7" s="22" t="inlineStr">

--- a/sheets/민요/검수/신 천안 삼거리.xlsx
+++ b/sheets/민요/검수/신 천안 삼거리.xlsx
@@ -65,10 +65,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="solid">

--- a/sheets/민요/검수/신 천안 삼거리.xlsx
+++ b/sheets/민요/검수/신 천안 삼거리.xlsx
@@ -1885,6 +1885,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1897,10 +1900,10 @@
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="102.95" customHeight="1">
+    <row r="2" ht="52.63" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -1915,7 +1918,7 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="3" ht="102.95" customHeight="1">
+    <row r="3" ht="117.4" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -1973,7 +1976,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="102.95" customHeight="1">
+    <row r="4" ht="117.4" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -2028,7 +2031,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="102.95" customHeight="1">
+    <row r="5" ht="117.4" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -2080,7 +2083,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="102.95" customHeight="1">
+    <row r="6" ht="117.4" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2136,7 +2139,7 @@
       </c>
       <c r="I6" s="26"/>
     </row>
-    <row r="7" ht="102.95" customHeight="1">
+    <row r="7" ht="117.4" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2195,7 +2198,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="102.95" customHeight="1">
+    <row r="8" ht="117.4" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -2252,7 +2255,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="102.95" customHeight="1">
+    <row r="9" ht="117.4" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -2305,7 +2308,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="102.95" customHeight="1">
+    <row r="10" ht="117.4" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -2366,6 +2369,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="100"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="76"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/신 천안 삼거리.xlsx
+++ b/sheets/민요/검수/신 천안 삼거리.xlsx
@@ -1890,13 +1890,13 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
